--- a/ID-RSS/output.xlsx
+++ b/ID-RSS/output.xlsx
@@ -41,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001D9E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1F5EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,10 +71,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,13 +449,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -461,7 +472,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tanishk</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -472,6 +483,756 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>student_0001.docx</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>student_0002.docx</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sneha Gupta</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0002</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>student_0003.docx</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Pooja Agarwal</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0003</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>student_0004.docx</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0004</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>student_0005.docx</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Yadav</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0005</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>student_0006.docx</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Saxena</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0006</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>student_0007.docx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0007</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>student_0008.docx</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Vikram Tiwari</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0008</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>student_0009.docx</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0009</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>student_0010.docx</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0010</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>student_0011.docx</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Ananya Reddy</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0011</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>student_0012.docx</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Harsh Malhotra</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0012</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>student_0013.docx</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Neha Patel</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0013</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>student_0014.docx</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Divya Mishra</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0014</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>student_0015.docx</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Divya Mishra</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0015</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>student_0016.docx</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0016</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>student_0017.docx</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Tanishk Bansal</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0017</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>student_0018.docx</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Karan Joshi</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0018</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>student_0019.docx</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Mehta</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0019</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>student_0020.docx</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Saxena</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0020</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>student_0021.docx</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Yadav</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0021</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>student_0022.docx</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Tanishk Bansal</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0022</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>student_0023.docx</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Mehta</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0023</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>student_0024.docx</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Sneha Gupta</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0024</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>student_0025.docx</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Harsh Malhotra</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0025</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>student_0026.docx</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Verma</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>student_0027.docx</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Harsh Malhotra</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0027</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>student_0028.docx</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Pooja Agarwal</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0028</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>student_0029.docx</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Rohit Mehta</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0029</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>student_0030.docx</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Mehta</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0030</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -494,7 +1255,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Extraction Summary</t>
         </is>
@@ -506,39 +1267,39 @@
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total files processed</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Fields extracted</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tanishk, Serial No.</t>
+          <t>Name, Serial No.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Fully extracted (100%)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Partial extractions</t>
         </is>
@@ -548,7 +1309,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Failed extractions</t>
         </is>
@@ -558,19 +1319,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Date &amp; Time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20 Mar 2026, 02:50 PM</t>
+          <t>20 Mar 2026, 03:24 PM</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Generated by</t>
         </is>

--- a/ID-RSS/output.xlsx
+++ b/ID-RSS/output.xlsx
@@ -41,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001D9E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1F5EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,10 +71,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,13 +449,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -461,7 +472,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tanishk</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -472,6 +483,756 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>student_0001.docx</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Divya Mishra</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>student_0002.docx</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Verma</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0002</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>student_0003.docx</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Anjali Singh</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0003</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>student_0004.docx</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Siddharth Nair</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0004</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>student_0005.docx</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Ritika Saxena</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0005</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>student_0006.docx</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Ananya Reddy</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0006</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>student_0007.docx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Tanishk Bansal</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0007</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>student_0008.docx</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Saxena</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0008</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>student_0009.docx</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Kavya Iyer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0009</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>student_0010.docx</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0010</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>student_0011.docx</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Pooja Agarwal</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0011</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>student_0012.docx</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Neha Patel</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0012</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>student_0013.docx</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Sneha Gupta</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0013</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>student_0014.docx</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Sneha Gupta</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0014</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>student_0015.docx</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Siddharth Nair</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0015</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>student_0016.docx</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Sneha Gupta</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0016</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>student_0017.docx</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Amit Kumar</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0017</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>student_0018.docx</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Kavya Iyer</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0018</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>student_0019.docx</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Neha Patel</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0019</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>student_0020.docx</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Ananya Reddy</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0020</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>student_0021.docx</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Harsh Malhotra</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0021</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>student_0022.docx</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Pooja Agarwal</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0022</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>student_0023.docx</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Ananya Reddy</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0023</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>student_0024.docx</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Simran Kaur</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0024</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>student_0025.docx</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Harsh Malhotra</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0025</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>student_0026.docx</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Pooja Agarwal</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>student_0027.docx</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Simran Kaur</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0027</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>student_0028.docx</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Vikram Tiwari</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0028</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>student_0029.docx</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Rahul Verma</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>STU-2024-0029</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>student_0030.docx</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Neha Patel</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>STU-2024-0030</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -494,7 +1255,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Extraction Summary</t>
         </is>
@@ -506,39 +1267,39 @@
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total files processed</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Fields extracted</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tanishk, Serial No.</t>
+          <t>Name, Serial No.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Fully extracted (100%)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Partial extractions</t>
         </is>
@@ -548,7 +1309,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Failed extractions</t>
         </is>
@@ -558,19 +1319,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Date &amp; Time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20 Mar 2026, 02:50 PM</t>
+          <t>20 Mar 2026, 03:41 PM</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Generated by</t>
         </is>
